--- a/eclipse-workspace/Website/src/test/resources/Qafox.xlsx
+++ b/eclipse-workspace/Website/src/test/resources/Qafox.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muhindhar S V\eclipse-workspace\Website\src\test\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB5C56D-8314-4407-A725-267674CFD34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{639E36AE-23EE-41B6-8D78-18F9E93B1557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{FED670D4-E846-475E-9DA6-44D917598E8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FED670D4-E846-475E-9DA6-44D917598E8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:K7"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
